--- a/MainTop/28.05.2026 Макс ВБ/p1.xlsx
+++ b/MainTop/28.05.2026 Макс ВБ/p1.xlsx
@@ -494,7 +494,7 @@
         <v>23</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>49.4</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>6.699999999999999</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="7">
